--- a/docs/protocols/DailyScrum_Vorlage.xlsx
+++ b/docs/protocols/DailyScrum_Vorlage.xlsx
@@ -464,13 +464,19 @@
   <dimension ref="A1:J13"/>
   <sheetFormatPr defaultRowHeight="15" defaultColWidth="7.75390625" customHeight="1"/>
   <cols>
+    <col min="1" max="1" width="11.8359375" customWidth="1"/>
+    <col min="2" max="2" width="9.9453125" customWidth="1"/>
+    <col min="3" max="3" width="11.8359375" customWidth="1"/>
+    <col min="4" max="4" width="11.390625" customWidth="1"/>
     <col min="9" max="9" width="52.875" customWidth="1"/>
     <col min="10" max="10" width="99.50390625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Datum:</t>
+        </is>
       </c>
       <c r="B1" t="s">
         <v>1</v>
